--- a/Config/Excel/Tables/技能配置表.xlsx
+++ b/Config/Excel/Tables/技能配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="8700"/>
+    <workbookView windowWidth="26955" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="SkillConfig" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>1|2</t>
+  </si>
+  <si>
+    <t>SkeletonAttack</t>
   </si>
 </sst>
 </file>
@@ -1042,8 +1045,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="14.875" customWidth="1"/>
@@ -1143,6 +1146,23 @@
       </c>
       <c r="F5" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>5000</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
